--- a/region/North-West-overview-grid.xlsx
+++ b/region/North-West-overview-grid.xlsx
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — North West — generated 8/14/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — North West — generated 8/17/2026</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       <c r="N17" s="5"/>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'3"' x 24'6"'</t>
+          <t xml:space="preserve">12'3" x 24'6"</t>
         </is>
       </c>
       <c r="P17" s="5"/>
@@ -2288,7 +2288,7 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48"'</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P22" s="4"/>
@@ -2594,7 +2594,7 @@
       <c r="N25" s="5"/>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P25" s="5"/>
@@ -2794,7 +2794,7 @@
       <c r="N27" s="5"/>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P27" s="5"/>
@@ -6294,7 +6294,7 @@
       <c r="N60" s="4"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16'' x 32"'</t>
+          <t xml:space="preserve">16' x 32'</t>
         </is>
       </c>
       <c r="P60" s="4"/>

--- a/region/North-West-overview-grid.xlsx
+++ b/region/North-West-overview-grid.xlsx
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — North West — generated 8/17/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — North West — generated 8/18/2026</t>
         </is>
       </c>
     </row>

--- a/region/North-West-overview-grid.xlsx
+++ b/region/North-West-overview-grid.xlsx
@@ -112,7 +112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD69"/>
+  <dimension ref="A1:AD68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -150,7 +150,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B  |  Region Overview information — North West — generated 8/18/2026</t>
+          <t xml:space="preserve">H-E-B  |  Region Overview information — North West — generated 8/28/2026</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1724,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">44515</t>
+          <t xml:space="preserve">5021</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
@@ -1749,61 +1749,61 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premier Panel</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">384654</t>
+          <t xml:space="preserve">380576</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 78 NS 0.47mi E/O Brown St F/E - 2</t>
+          <t xml:space="preserve">Hwy 121 NS 0.2mi W/O Legacy Dr F/W - 1</t>
         </is>
       </c>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="11">
-        <v>33.022664</v>
+        <v>33.081719</v>
       </c>
       <c r="L17" s="11">
-        <v>-96.522918</v>
+        <v>-96.855608</v>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'3" x 24'6"</t>
+          <t xml:space="preserve">14'0"' x 48'0"'</t>
         </is>
       </c>
       <c r="P17" s="5"/>
       <c r="Q17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO</t>
+          <t xml:space="preserve">121 HV</t>
         </is>
       </c>
       <c r="R17" s="7">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="S17" s="7">
-        <v>46257</v>
+        <v>46474</v>
       </c>
       <c r="T17" s="5"/>
       <c r="U17" s="5">
-        <v>91801</v>
+        <v>341564</v>
       </c>
       <c r="V17" s="9">
-        <v>1890</v>
+        <v>13080</v>
       </c>
       <c r="W17" s="9"/>
       <c r="X17" s="5"/>
       <c r="Y17" s="5">
-        <v>1.8</v>
+        <v>5</v>
       </c>
       <c r="Z17" s="13" t="inlineStr">
         <is>
@@ -1812,21 +1812,21 @@
       </c>
       <c r="AA17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO: Now Open</t>
+          <t xml:space="preserve">Pound for Pound</t>
         </is>
       </c>
       <c r="AB17" s="5"/>
       <c r="AC17" s="7"/>
       <c r="AD17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5021</t>
+          <t xml:space="preserve">6212</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1854,23 +1854,19 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">380576</t>
-        </is>
-      </c>
+      <c r="G18" s="4"/>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 121 NS 0.2mi W/O Legacy Dr F/W - 1</t>
+          <t xml:space="preserve">Hwy 80 NS 0.3mi E/O FM 740 F/W - 1</t>
         </is>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
       <c r="K18" s="10">
-        <v>33.081719</v>
+        <v>32.753641</v>
       </c>
       <c r="L18" s="10">
-        <v>-96.855608</v>
+        <v>-96.463206</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -1880,32 +1876,36 @@
       <c r="N18" s="4"/>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'0"' x 48'0"'</t>
+          <t xml:space="preserve">10'' x 40''</t>
         </is>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">121 HV</t>
+          <t xml:space="preserve">HV HWY80</t>
         </is>
       </c>
       <c r="R18" s="6">
         <v>46209</v>
       </c>
       <c r="S18" s="6">
-        <v>46474</v>
-      </c>
-      <c r="T18" s="4"/>
+        <v>46572</v>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1302134-NSG-HEB CHI DFW 2026-06-09 10_50 CDT_encrypted_.pdf</t>
+        </is>
+      </c>
       <c r="U18" s="4">
-        <v>341564</v>
+        <v>140145</v>
       </c>
       <c r="V18" s="8">
-        <v>13080</v>
+        <v>2000</v>
       </c>
       <c r="W18" s="8"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="Z18" s="12" t="inlineStr">
         <is>
@@ -1921,14 +1921,14 @@
       <c r="AC18" s="6"/>
       <c r="AD18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: Delivery</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6212</t>
+          <t xml:space="preserve">6782</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1956,19 +1956,23 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G19" s="5"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">381230</t>
+        </is>
+      </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 80 NS 0.3mi E/O FM 740 F/W - 1</t>
+          <t xml:space="preserve">SH 121 (Sam Rayburn Tollway) NS 0.56mi E/O Hillcrest Rd F/W - 1</t>
         </is>
       </c>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="11">
-        <v>32.753641</v>
+        <v>33.108205</v>
       </c>
       <c r="L19" s="11">
-        <v>-96.463206</v>
+        <v>-96.780131</v>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
@@ -1978,36 +1982,32 @@
       <c r="N19" s="5"/>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10'' x 40''</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P19" s="5"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV HWY80</t>
+          <t xml:space="preserve">121 HV</t>
         </is>
       </c>
       <c r="R19" s="7">
         <v>46209</v>
       </c>
       <c r="S19" s="7">
-        <v>46572</v>
-      </c>
-      <c r="T19" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1302134-NSG-HEB CHI DFW 2026-06-09 10_50 CDT_encrypted_.pdf</t>
-        </is>
-      </c>
+        <v>46418</v>
+      </c>
+      <c r="T19" s="5"/>
       <c r="U19" s="5">
-        <v>140145</v>
+        <v>298768</v>
       </c>
       <c r="V19" s="9">
-        <v>2000</v>
+        <v>14940</v>
       </c>
       <c r="W19" s="9"/>
       <c r="X19" s="5"/>
       <c r="Y19" s="5">
-        <v>1.1</v>
+        <v>4.9</v>
       </c>
       <c r="Z19" s="13" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AA19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB19" s="5"/>
@@ -2030,7 +2030,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6782</t>
+          <t xml:space="preserve">78346</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -2060,21 +2060,21 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">381230</t>
+          <t xml:space="preserve">551265</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SH 121 (Sam Rayburn Tollway) NS 0.56mi E/O Hillcrest Rd F/W - 1</t>
+          <t xml:space="preserve">West Fwy (I-30) SS 0.6mi W/O Linkcrest F/W - 2</t>
         </is>
       </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="10">
-        <v>33.108205</v>
+        <v>32.720316</v>
       </c>
       <c r="L20" s="10">
-        <v>-96.780131</v>
+        <v>-97.544309</v>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
       <c r="N20" s="4"/>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14'' x 48"'</t>
         </is>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">121 HV</t>
+          <t xml:space="preserve">1-30 HV</t>
         </is>
       </c>
       <c r="R20" s="6">
         <v>46209</v>
       </c>
       <c r="S20" s="6">
-        <v>46418</v>
+        <v>46530</v>
       </c>
       <c r="T20" s="4"/>
       <c r="U20" s="4">
-        <v>298768</v>
+        <v>202226</v>
       </c>
       <c r="V20" s="8">
-        <v>14940</v>
+        <v>3500</v>
       </c>
       <c r="W20" s="8"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4">
-        <v>4.9</v>
+        <v>9.3</v>
       </c>
       <c r="Z20" s="12" t="inlineStr">
         <is>
@@ -2118,21 +2118,21 @@
       </c>
       <c r="AA20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">We have marinated meats</t>
         </is>
       </c>
       <c r="AB20" s="4"/>
       <c r="AC20" s="6"/>
       <c r="AD20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Delivery</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78346</t>
+          <t xml:space="preserve">78883</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -2162,37 +2162,37 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">551265</t>
+          <t xml:space="preserve">30988268</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West Fwy (I-30) SS 0.6mi W/O Linkcrest F/W - 2</t>
+          <t xml:space="preserve">Hwy 190 NS 0.5mi E/O Merritt Rd F/E - 1</t>
         </is>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="11">
-        <v>32.720316</v>
+        <v>32.947674</v>
       </c>
       <c r="L21" s="11">
-        <v>-97.544309</v>
+        <v>-96.561838</v>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48"'</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P21" s="5"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1-30 HV</t>
+          <t xml:space="preserve">I-90 HV</t>
         </is>
       </c>
       <c r="R21" s="7">
@@ -2203,15 +2203,15 @@
       </c>
       <c r="T21" s="5"/>
       <c r="U21" s="5">
-        <v>202226</v>
+        <v>265532</v>
       </c>
       <c r="V21" s="9">
-        <v>3500</v>
+        <v>3365</v>
       </c>
       <c r="W21" s="9"/>
       <c r="X21" s="5"/>
       <c r="Y21" s="5">
-        <v>9.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z21" s="13" t="inlineStr">
         <is>
@@ -2220,21 +2220,21 @@
       </c>
       <c r="AA21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">We have marinated meats</t>
+          <t xml:space="preserve">GO: Now Open</t>
         </is>
       </c>
       <c r="AB21" s="5"/>
       <c r="AC21" s="7"/>
       <c r="AD21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78883</t>
+          <t xml:space="preserve">78885</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -2264,21 +2264,21 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">30988268</t>
+          <t xml:space="preserve">30988270</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 190 NS 0.5mi E/O Merritt Rd F/E - 1</t>
+          <t xml:space="preserve">Hwy 190 NS 0.6mi E/O Merritt Rd F/E - 1</t>
         </is>
       </c>
       <c r="I22" s="4"/>
       <c r="J22" s="4"/>
       <c r="K22" s="10">
-        <v>32.947674</v>
+        <v>32.947259</v>
       </c>
       <c r="L22" s="10">
-        <v>-96.561838</v>
+        <v>-96.561019</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       <c r="N22" s="4"/>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">14'' x 48"'</t>
         </is>
       </c>
       <c r="P22" s="4"/>
@@ -2298,17 +2298,17 @@
         </is>
       </c>
       <c r="R22" s="6">
-        <v>46209</v>
+        <v>46391</v>
       </c>
       <c r="S22" s="6">
-        <v>46530</v>
+        <v>46754</v>
       </c>
       <c r="T22" s="4"/>
       <c r="U22" s="4">
-        <v>265532</v>
+        <v>174763</v>
       </c>
       <c r="V22" s="8">
-        <v>3365</v>
+        <v>3000</v>
       </c>
       <c r="W22" s="8"/>
       <c r="X22" s="4"/>
@@ -2322,21 +2322,21 @@
       </c>
       <c r="AA22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO: Now Open</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="AB22" s="4"/>
       <c r="AC22" s="6"/>
       <c r="AD22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78885</t>
+          <t xml:space="preserve">78898</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -2364,23 +2364,19 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30988270</t>
-        </is>
-      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 190 NS 0.6mi E/O Merritt Rd F/E - 1</t>
+          <t xml:space="preserve">Hwy 380 NS 0.1mi W/O Magnolia Blvd F/E - 2</t>
         </is>
       </c>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="11">
-        <v>32.947259</v>
+        <v>33.22047</v>
       </c>
       <c r="L23" s="11">
-        <v>-96.561019</v>
+        <v>-96.916501</v>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
@@ -2390,32 +2386,36 @@
       <c r="N23" s="5"/>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48"'</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-90 HV</t>
+          <t xml:space="preserve">HV 380</t>
         </is>
       </c>
       <c r="R23" s="7">
-        <v>46391</v>
+        <v>46195</v>
       </c>
       <c r="S23" s="7">
-        <v>46754</v>
-      </c>
-      <c r="T23" s="5"/>
+        <v>46558</v>
+      </c>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1302134-NSG-HEB CHI DFW 2026-06-09 10_50 CDT_encrypted_.pdf</t>
+        </is>
+      </c>
       <c r="U23" s="5">
-        <v>174763</v>
+        <v>174776</v>
       </c>
       <c r="V23" s="9">
-        <v>3000</v>
+        <v>3540</v>
       </c>
       <c r="W23" s="9"/>
       <c r="X23" s="5"/>
       <c r="Y23" s="5">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z23" s="13" t="inlineStr">
         <is>
@@ -2424,21 +2424,21 @@
       </c>
       <c r="AA23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">Pound for Pound</t>
         </is>
       </c>
       <c r="AB23" s="5"/>
       <c r="AC23" s="7"/>
       <c r="AD23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78898</t>
+          <t xml:space="preserve">78924</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -2466,58 +2466,58 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G24" s="4"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50617077</t>
+        </is>
+      </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 380 NS 0.1mi W/O Magnolia Blvd F/E - 2</t>
+          <t xml:space="preserve">LBJ Fwy (I-635) NS 0.7mi E/O Hwy 121 F/W - 1</t>
         </is>
       </c>
       <c r="I24" s="4"/>
       <c r="J24" s="4"/>
       <c r="K24" s="10">
-        <v>33.22047</v>
+        <v>32.947504</v>
       </c>
       <c r="L24" s="10">
-        <v>-96.916501</v>
+        <v>-97.02687</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N24" s="4"/>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P24" s="4"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HV 380</t>
+          <t xml:space="preserve">GO</t>
         </is>
       </c>
       <c r="R24" s="6">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="S24" s="6">
-        <v>46558</v>
-      </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1302134-NSG-HEB CHI DFW 2026-06-09 10_50 CDT_encrypted_.pdf</t>
-        </is>
-      </c>
+        <v>46264</v>
+      </c>
+      <c r="T24" s="4"/>
       <c r="U24" s="4">
-        <v>174776</v>
+        <v>223231</v>
       </c>
       <c r="V24" s="8">
-        <v>3540</v>
+        <v>14780</v>
       </c>
       <c r="W24" s="8"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="Z24" s="12" t="inlineStr">
         <is>
@@ -2526,21 +2526,21 @@
       </c>
       <c r="AA24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">GO: Now Open</t>
         </is>
       </c>
       <c r="AB24" s="4"/>
       <c r="AC24" s="6"/>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78924</t>
+          <t xml:space="preserve">78987</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -2568,53 +2568,53 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50617077</t>
-        </is>
-      </c>
+      <c r="G25" s="5"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LBJ Fwy (I-635) NS 0.7mi E/O Hwy 121 F/W - 1</t>
+          <t xml:space="preserve">Hwy 190 SS 0.4mi E/O Merritt Rd F/E - 1</t>
         </is>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="11">
-        <v>32.947504</v>
+        <v>32.947534</v>
       </c>
       <c r="L25" s="11">
-        <v>-97.02687</v>
+        <v>-96.563916</v>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P25" s="5"/>
       <c r="Q25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO</t>
+          <t xml:space="preserve">I-90 HV</t>
         </is>
       </c>
       <c r="R25" s="7">
-        <v>46209</v>
+        <v>46335</v>
       </c>
       <c r="S25" s="7">
-        <v>46264</v>
-      </c>
-      <c r="T25" s="5"/>
+        <v>46698</v>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1302134-NSG-HEB CHI DFW 2026-06-09 10_50 CDT_encrypted_.pdf</t>
+        </is>
+      </c>
       <c r="U25" s="5">
-        <v>223231</v>
+        <v>154270</v>
       </c>
       <c r="V25" s="9">
-        <v>14780</v>
+        <v>3000</v>
       </c>
       <c r="W25" s="9"/>
       <c r="X25" s="5"/>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="AA25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO: Now Open</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="AB25" s="5"/>
@@ -2642,7 +2642,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">78987</t>
+          <t xml:space="preserve">78991</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -2673,16 +2673,16 @@
       <c r="G26" s="4"/>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 190 SS 0.4mi E/O Merritt Rd F/E - 1</t>
+          <t xml:space="preserve">Hwy 190 SS 0.3mi E/O Merritt Rd F/E - 1</t>
         </is>
       </c>
       <c r="I26" s="4"/>
       <c r="J26" s="4"/>
       <c r="K26" s="10">
-        <v>32.947534</v>
+        <v>32.948055</v>
       </c>
       <c r="L26" s="10">
-        <v>-96.563916</v>
+        <v>-96.564974</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
       <c r="N26" s="4"/>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P26" s="4"/>
@@ -2702,10 +2702,10 @@
         </is>
       </c>
       <c r="R26" s="6">
-        <v>46335</v>
+        <v>46223</v>
       </c>
       <c r="S26" s="6">
-        <v>46698</v>
+        <v>46586</v>
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="U26" s="4">
-        <v>154270</v>
+        <v>151134</v>
       </c>
       <c r="V26" s="8">
         <v>3000</v>
@@ -2730,36 +2730,36 @@
       </c>
       <c r="AA26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">GO: Now Open</t>
         </is>
       </c>
       <c r="AB26" s="4"/>
       <c r="AC26" s="6"/>
       <c r="AD26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">GO: Now Open</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">78991</t>
+          <t xml:space="preserve">216-6001A</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clear Channel Outdoor</t>
+          <t xml:space="preserve">Firewheel Outdoor</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Samantha Idler</t>
+          <t xml:space="preserve">Chris Francis</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">samanthaidler@clearchannel.com</t>
+          <t xml:space="preserve">chris@firewheeloutdoor.com</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -2769,84 +2769,98 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital-Bulletin</t>
         </is>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 190 SS 0.3mi E/O Merritt Rd F/E - 1</t>
-        </is>
-      </c>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
+          <t xml:space="preserve">2698 North George Bush Highway — Firewheel Town Center - President Geo. Bush Tollway (Hwy. 190) n/l
+1 mi. e/o Hwy. 78 (Lavon Dr.)
+Garland Texas (East Face and West Face)</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Garland</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75040</t>
+        </is>
+      </c>
       <c r="K27" s="11">
-        <v>32.948055</v>
+        <v>32.948633</v>
       </c>
       <c r="L27" s="11">
-        <v>-96.564974</v>
+        <v>-96.604543</v>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">East</t>
         </is>
       </c>
-      <c r="N27" s="5"/>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
-        </is>
-      </c>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I-90 HV</t>
-        </is>
-      </c>
+          <t xml:space="preserve">12’6”x42’</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q27" s="5"/>
       <c r="R27" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="S27" s="7">
-        <v>46586</v>
+        <v>46327</v>
       </c>
       <c r="T27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302134-NSG-HEB CHI DFW 2026-06-09 10_50 CDT_encrypted_.pdf</t>
+          <t xml:space="preserve">HEB.FODN.2026 executed.pdf</t>
         </is>
       </c>
       <c r="U27" s="5">
-        <v>151134</v>
+        <v>18452</v>
       </c>
       <c r="V27" s="9">
-        <v>3000</v>
+        <v>2350</v>
       </c>
       <c r="W27" s="9"/>
-      <c r="X27" s="5"/>
+      <c r="X27" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📷 Panel Photo</t>
+        </is>
+      </c>
       <c r="Y27" s="5">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="Z27" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA27" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO: Now Open</t>
-        </is>
-      </c>
+      <c r="AA27" s="5"/>
       <c r="AB27" s="5"/>
       <c r="AC27" s="7"/>
       <c r="AD27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">GO: Now Open</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">216-6001A</t>
+          <t xml:space="preserve">216-6002A</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2877,9 +2891,9 @@
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2698 North George Bush Highway — Firewheel Town Center - President Geo. Bush Tollway (Hwy. 190) n/l
-1 mi. e/o Hwy. 78 (Lavon Dr.)
-Garland Texas (East Face and West Face)</t>
+          <t xml:space="preserve">9 Town Center Boulevard — Firewheel Town Center-Hwy. 78 (Lavon Dr.) e/l .2 mi. n/o
+President Geo. Bush Tollway (Hwy. 190)
+Garland Texas (North Face and West Face)</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2893,14 +2907,14 @@
         </is>
       </c>
       <c r="K28" s="10">
-        <v>32.948633</v>
+        <v>32.952932</v>
       </c>
       <c r="L28" s="10">
-        <v>-96.604543</v>
+        <v>-96.61777</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2931,10 +2945,10 @@
         </is>
       </c>
       <c r="U28" s="4">
-        <v>18452</v>
+        <v>165235</v>
       </c>
       <c r="V28" s="8">
-        <v>2350</v>
+        <v>2700</v>
       </c>
       <c r="W28" s="8"/>
       <c r="X28" s="12" t="inlineStr">
@@ -2943,7 +2957,7 @@
         </is>
       </c>
       <c r="Y28" s="4">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Z28" s="12" t="inlineStr">
         <is>
@@ -2955,29 +2969,25 @@
       <c r="AC28" s="6"/>
       <c r="AD28" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: Delivery</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">216-6002A</t>
+          <t xml:space="preserve">635L</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Firewheel Outdoor</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chris Francis</t>
-        </is>
-      </c>
+          <t xml:space="preserve">J R Media Services</t>
+        </is>
+      </c>
+      <c r="C29" s="5"/>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">chris@firewheeloutdoor.com</t>
+          <t xml:space="preserve">james.robison0821@gmail.com</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2987,109 +2997,99 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital-Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 Town Center Boulevard — Firewheel Town Center-Hwy. 78 (Lavon Dr.) e/l .2 mi. n/o
-President Geo. Bush Tollway (Hwy. 190)
-Garland Texas (North Face and West Face)</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Garland</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75040</t>
-        </is>
-      </c>
+          <t xml:space="preserve">I635 .4mi w/o Coit, .7mi w/o US75 (High 5)</t>
+        </is>
+      </c>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
       <c r="K29" s="11">
-        <v>32.952932</v>
+        <v>32.9235</v>
       </c>
       <c r="L29" s="11">
-        <v>-96.61777</v>
+        <v>-96.7745</v>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N29" s="5"/>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">12’6”x42’</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q29" s="5"/>
+          <t xml:space="preserve">16'' x 32"'</t>
+        </is>
+      </c>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">635 HV</t>
+        </is>
+      </c>
       <c r="R29" s="7">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="S29" s="7">
-        <v>46327</v>
+        <v>46530</v>
       </c>
       <c r="T29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEB.FODN.2026 executed.pdf</t>
+          <t xml:space="preserve">Complete_with_Docusign_635L_H-E-B_Takeover_7.pdf</t>
         </is>
       </c>
       <c r="U29" s="5">
-        <v>165235</v>
+        <v>1479573</v>
       </c>
       <c r="V29" s="9">
-        <v>2700</v>
+        <v>5000</v>
       </c>
       <c r="W29" s="9"/>
-      <c r="X29" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📷 Panel Photo</t>
-        </is>
-      </c>
+      <c r="X29" s="5"/>
       <c r="Y29" s="5">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z29" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA29" s="5"/>
+      <c r="AA29" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">See what all the guac is about</t>
+        </is>
+      </c>
       <c r="AB29" s="5"/>
       <c r="AC29" s="7"/>
       <c r="AD29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Delivery</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">635L</t>
+          <t xml:space="preserve">10652</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">J R Media Services</t>
-        </is>
-      </c>
-      <c r="C30" s="4"/>
+          <t xml:space="preserve">Lamar Advertising</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brendolyn O'Connor</t>
+        </is>
+      </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">james.robison0821@gmail.com</t>
+          <t xml:space="preserve">boconnor@lamar.com</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -3099,61 +3099,69 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Static Bulletin</t>
         </is>
       </c>
       <c r="G30" s="4"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I635 .4mi w/o Coit, .7mi w/o US75 (High 5)</t>
+          <t xml:space="preserve">HWY 183 E/S .1 MI N/O MOCKINGBIRD LANE - 10652</t>
         </is>
       </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4"/>
       <c r="K30" s="10">
-        <v>32.9235</v>
+        <v>32.81899</v>
       </c>
       <c r="L30" s="10">
-        <v>-96.7745</v>
+        <v>-96.87201</v>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
-        </is>
-      </c>
-      <c r="N30" s="4"/>
+          <t xml:space="preserve">Southeast</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16'' x 32"'</t>
-        </is>
-      </c>
-      <c r="P30" s="4"/>
+          <t xml:space="preserve">14' x 48'</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">635 HV</t>
+          <t xml:space="preserve">TX-183 HV</t>
         </is>
       </c>
       <c r="R30" s="6">
-        <v>46209</v>
+        <v>46181</v>
       </c>
       <c r="S30" s="6">
-        <v>46530</v>
+        <v>46460</v>
       </c>
       <c r="T30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complete_with_Docusign_635L_H-E-B_Takeover_7.pdf</t>
+          <t xml:space="preserve">1248526-SAT-HEB SAT 2026-01-22 15_10 CST.pdf</t>
         </is>
       </c>
       <c r="U30" s="4">
-        <v>1479573</v>
+        <v>582320</v>
       </c>
       <c r="V30" s="8">
-        <v>5000</v>
+        <v>6568</v>
       </c>
       <c r="W30" s="8"/>
       <c r="X30" s="4"/>
       <c r="Y30" s="4">
-        <v>7.4</v>
+        <v>8.9</v>
       </c>
       <c r="Z30" s="12" t="inlineStr">
         <is>
@@ -3169,14 +3177,14 @@
       <c r="AC30" s="6"/>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10652</t>
+          <t xml:space="preserve">114</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -3201,33 +3209,33 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
-        </is>
-      </c>
-      <c r="G31" s="5"/>
+          <t xml:space="preserve">Digital Bulletin</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14922909</t>
+        </is>
+      </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HWY 183 E/S .1 MI N/O MOCKINGBIRD LANE - 10652</t>
+          <t xml:space="preserve">HWY 287, E/S, 1.5 MI N/O FM 157, N/F (between I-20 and SH-360)</t>
         </is>
       </c>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="11">
-        <v>32.81899</v>
+        <v>32.61676</v>
       </c>
       <c r="L31" s="11">
-        <v>-96.87201</v>
+        <v>-97.16233</v>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Southeast</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Northwest</t>
+        </is>
+      </c>
+      <c r="N31" s="5"/>
       <c r="O31" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
@@ -3238,55 +3246,47 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TX-183 HV</t>
-        </is>
-      </c>
+      <c r="Q31" s="5"/>
       <c r="R31" s="7">
-        <v>46181</v>
+        <v>46244</v>
       </c>
       <c r="S31" s="7">
-        <v>46460</v>
-      </c>
-      <c r="T31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248526-SAT-HEB SAT 2026-01-22 15_10 CST.pdf</t>
-        </is>
-      </c>
+        <v>46327</v>
+      </c>
+      <c r="T31" s="5"/>
       <c r="U31" s="5">
-        <v>582320</v>
+        <v>137437</v>
       </c>
       <c r="V31" s="9">
-        <v>6568</v>
+        <v>2895</v>
       </c>
       <c r="W31" s="9"/>
-      <c r="X31" s="5"/>
+      <c r="X31" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📷 Panel Photo</t>
+        </is>
+      </c>
       <c r="Y31" s="5">
-        <v>8.9</v>
+        <v>4.3</v>
       </c>
       <c r="Z31" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA31" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">See what all the guac is about</t>
-        </is>
-      </c>
+      <c r="AA31" s="5"/>
       <c r="AB31" s="5"/>
       <c r="AC31" s="7"/>
       <c r="AD31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">To Be Determined</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">114</t>
+          <t xml:space="preserve">2023</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -3311,33 +3311,33 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14922909</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Static Bulletin</t>
+        </is>
+      </c>
+      <c r="G32" s="4"/>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HWY 287, E/S, 1.5 MI N/O FM 157, N/F (between I-20 and SH-360)</t>
+          <t xml:space="preserve">I-30 .5 MI E/O COOKS LN S/S - 2023</t>
         </is>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
       <c r="K32" s="10">
-        <v>32.61676</v>
+        <v>32.75935</v>
       </c>
       <c r="L32" s="10">
-        <v>-97.16233</v>
+        <v>-97.17904</v>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Northwest</t>
-        </is>
-      </c>
-      <c r="N32" s="4"/>
+          <t xml:space="preserve">West</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">14' x 48'</t>
@@ -3348,47 +3348,55 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I-30 HV</t>
+        </is>
+      </c>
       <c r="R32" s="6">
-        <v>46244</v>
+        <v>46223</v>
       </c>
       <c r="S32" s="6">
-        <v>46327</v>
-      </c>
-      <c r="T32" s="4"/>
+        <v>46474</v>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">H-E-B #5569069 - signed.pdf</t>
+        </is>
+      </c>
       <c r="U32" s="4">
-        <v>137437</v>
+        <v>603686</v>
       </c>
       <c r="V32" s="8">
-        <v>2895</v>
+        <v>4599</v>
       </c>
       <c r="W32" s="8"/>
-      <c r="X32" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📷 Panel Photo</t>
-        </is>
-      </c>
+      <c r="X32" s="4"/>
       <c r="Y32" s="4">
-        <v>4.3</v>
+        <v>8.5</v>
       </c>
       <c r="Z32" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA32" s="4"/>
+      <c r="AA32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Psst... we have brisket queso</t>
+        </is>
+      </c>
       <c r="AB32" s="4"/>
       <c r="AC32" s="6"/>
       <c r="AD32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">To Be Determined</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023</t>
+          <t xml:space="preserve">2433</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -3413,22 +3421,26 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Static Bulletin</t>
-        </is>
-      </c>
-      <c r="G33" s="5"/>
+          <t xml:space="preserve">Bulletin</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">392291</t>
+        </is>
+      </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-30 .5 MI E/O COOKS LN S/S - 2023</t>
+          <t xml:space="preserve">I-20 @ Lake Shore Dr, Exit 413, S/S</t>
         </is>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="11">
-        <v>32.75935</v>
+        <v>32.75445</v>
       </c>
       <c r="L33" s="11">
-        <v>-97.17904</v>
+        <v>-97.70218</v>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
@@ -3450,55 +3462,51 @@
           <t xml:space="preserve">Y</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">I-30 HV</t>
-        </is>
-      </c>
+      <c r="Q33" s="5"/>
       <c r="R33" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="S33" s="7">
-        <v>46474</v>
+        <v>46495</v>
       </c>
       <c r="T33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">H-E-B #5569069 - signed.pdf</t>
+          <t xml:space="preserve">11.2.26 H-E-B - Walsh Ranch C#5648706.pdf</t>
         </is>
       </c>
       <c r="U33" s="5">
-        <v>603686</v>
+        <v>294900</v>
       </c>
       <c r="V33" s="9">
-        <v>4599</v>
+        <v>3749</v>
       </c>
       <c r="W33" s="9"/>
-      <c r="X33" s="5"/>
+      <c r="X33" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📷 Panel Photo</t>
+        </is>
+      </c>
       <c r="Y33" s="5">
-        <v>8.5</v>
+        <v>0.4</v>
       </c>
       <c r="Z33" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA33" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psst... we have brisket queso</t>
-        </is>
-      </c>
+      <c r="AA33" s="5"/>
       <c r="AB33" s="5"/>
       <c r="AC33" s="7"/>
       <c r="AD33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">Cowboys: Delivery</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2433</t>
+          <t xml:space="preserve">2465</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -3528,87 +3536,83 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">392291</t>
+          <t xml:space="preserve">263993</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-20 @ Lake Shore Dr, Exit 413, S/S</t>
+          <t xml:space="preserve">W/S FM 195 AT STAN SCHL LP F/S</t>
         </is>
       </c>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="10">
-        <v>32.75445</v>
+        <v>31.0788</v>
       </c>
       <c r="L34" s="10">
-        <v>-97.70218</v>
+        <v>-97.7585</v>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">South</t>
+        </is>
+      </c>
+      <c r="N34" s="4"/>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q34" s="4"/>
+          <t xml:space="preserve">14'' x 48''</t>
+        </is>
+      </c>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLA</t>
+        </is>
+      </c>
       <c r="R34" s="6">
-        <v>46244</v>
+        <v>46195</v>
       </c>
       <c r="S34" s="6">
-        <v>46495</v>
+        <v>47286</v>
       </c>
       <c r="T34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.2.26 H-E-B - Walsh Ranch C#5648706.pdf</t>
+          <t xml:space="preserve">Lamar Contract #5580765 HEB_encrypted_.pdf</t>
         </is>
       </c>
       <c r="U34" s="4">
-        <v>294900</v>
+        <v>57009</v>
       </c>
       <c r="V34" s="8">
-        <v>3749</v>
+        <v>1250</v>
       </c>
       <c r="W34" s="8"/>
-      <c r="X34" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📷 Panel Photo</t>
-        </is>
-      </c>
+      <c r="X34" s="4"/>
       <c r="Y34" s="4">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="Z34" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA34" s="4"/>
+      <c r="AA34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
       <c r="AB34" s="4"/>
       <c r="AC34" s="6"/>
       <c r="AD34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Delivery</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2465</t>
+          <t xml:space="preserve">2527</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
@@ -3638,28 +3642,32 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">263993</t>
+          <t xml:space="preserve">392346</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">W/S FM 195 AT STAN SCHL LP F/S</t>
+          <t xml:space="preserve">SH-121 N/O FM 157, E/S</t>
         </is>
       </c>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="11">
-        <v>31.0788</v>
+        <v>32.8695</v>
       </c>
       <c r="L35" s="11">
-        <v>-97.7585</v>
+        <v>-97.0995</v>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">South</t>
         </is>
       </c>
-      <c r="N35" s="5"/>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">14'' x 48''</t>
@@ -3668,30 +3676,30 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLA</t>
+          <t xml:space="preserve">121 HV</t>
         </is>
       </c>
       <c r="R35" s="7">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="S35" s="7">
-        <v>47286</v>
+        <v>46565</v>
       </c>
       <c r="T35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Contract #5580765 HEB_encrypted_.pdf</t>
+          <t xml:space="preserve">7.6.26 HEB DFW Perm 2026 (13234) C#5625750 (1).pdf</t>
         </is>
       </c>
       <c r="U35" s="5">
-        <v>57009</v>
+        <v>220168</v>
       </c>
       <c r="V35" s="9">
-        <v>1250</v>
+        <v>12343</v>
       </c>
       <c r="W35" s="9"/>
       <c r="X35" s="5"/>
       <c r="Y35" s="5">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Z35" s="13" t="inlineStr">
         <is>
@@ -3714,22 +3722,22 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2527</t>
+          <t xml:space="preserve">1012B</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lamar Advertising</t>
+          <t xml:space="preserve">Media Eyes</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brendolyn O'Connor</t>
+          <t xml:space="preserve">Michelle Ramsey</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">boconnor@lamar.com</t>
+          <t xml:space="preserve">michelle@outdooradvertiser.com</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -3744,87 +3752,71 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">392346</t>
+          <t xml:space="preserve">30982713</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SH-121 N/O FM 157, E/S</t>
+          <t xml:space="preserve">LBJ Frwy n/l 1 mi e/o Beltline Rd.</t>
         </is>
       </c>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="10">
-        <v>32.8695</v>
+        <v>32.920332</v>
       </c>
       <c r="L36" s="10">
-        <v>-97.0995</v>
+        <v>-96.97629</v>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">West</t>
+        </is>
+      </c>
+      <c r="N36" s="4"/>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">12'' x 40''</t>
         </is>
       </c>
       <c r="P36" s="4"/>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121 HV</t>
-        </is>
-      </c>
+      <c r="Q36" s="4"/>
       <c r="R36" s="6">
         <v>46209</v>
       </c>
       <c r="S36" s="6">
-        <v>46565</v>
+        <v>46383</v>
       </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.6.26 HEB DFW Perm 2026 (13234) C#5625750 (1).pdf</t>
+          <t xml:space="preserve">1012B.jpg</t>
         </is>
       </c>
       <c r="U36" s="4">
-        <v>220168</v>
+        <v>82220</v>
       </c>
       <c r="V36" s="8">
-        <v>12343</v>
+        <v>4001.54</v>
       </c>
       <c r="W36" s="8"/>
       <c r="X36" s="4"/>
       <c r="Y36" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
+      <c r="AA36" s="4"/>
       <c r="AB36" s="4"/>
       <c r="AC36" s="6"/>
-      <c r="AD36" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
-        </is>
-      </c>
+      <c r="AD36" s="4"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1012B</t>
+          <t xml:space="preserve">1013A</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -3854,25 +3846,25 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">30982713</t>
+          <t xml:space="preserve">30982719</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LBJ Frwy n/l 1 mi e/o Beltline Rd.</t>
+          <t xml:space="preserve">LBJ Frwy. (Interstate 635) n/l 0.7 mi. w/o N. MacArthur Blvd.</t>
         </is>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="11">
-        <v>32.920332</v>
+        <v>32.918908</v>
       </c>
       <c r="L37" s="11">
-        <v>-96.97629</v>
+        <v>-96.969277</v>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N37" s="5"/>
@@ -3887,23 +3879,23 @@
         <v>46209</v>
       </c>
       <c r="S37" s="7">
-        <v>46383</v>
+        <v>46628</v>
       </c>
       <c r="T37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1012B.jpg</t>
+          <t xml:space="preserve">1013A.jpg</t>
         </is>
       </c>
       <c r="U37" s="5">
-        <v>82220</v>
+        <v>294625</v>
       </c>
       <c r="V37" s="9">
-        <v>4001.54</v>
+        <v>3787.55</v>
       </c>
       <c r="W37" s="9"/>
       <c r="X37" s="5"/>
       <c r="Y37" s="5">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Z37" s="13" t="inlineStr">
         <is>
@@ -3918,22 +3910,22 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013A</t>
+          <t xml:space="preserve">2_7166O</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Media Eyes</t>
+          <t xml:space="preserve">Outfront Media</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michelle Ramsey</t>
+          <t xml:space="preserve">Sammy Tamporello</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">michelle@outdooradvertiser.com</t>
+          <t xml:space="preserve">sammy.tamporello@outfront.com</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -3946,23 +3938,19 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30982719</t>
-        </is>
-      </c>
+      <c r="G38" s="4"/>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">LBJ Frwy. (Interstate 635) n/l 0.7 mi. w/o N. MacArthur Blvd.</t>
+          <t xml:space="preserve">LBJ (635) .2Mi W/O Plano Road N/S F/E</t>
         </is>
       </c>
       <c r="I38" s="4"/>
       <c r="J38" s="4"/>
       <c r="K38" s="10">
-        <v>32.918908</v>
+        <v>32.888565</v>
       </c>
       <c r="L38" s="10">
-        <v>-96.969277</v>
+        <v>-96.704219</v>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
@@ -3972,47 +3960,59 @@
       <c r="N38" s="4"/>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'' x 40''</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">635 HV</t>
+        </is>
+      </c>
       <c r="R38" s="6">
-        <v>46209</v>
+        <v>46181</v>
       </c>
       <c r="S38" s="6">
-        <v>46628</v>
+        <v>46544</v>
       </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013A.jpg</t>
+          <t xml:space="preserve">4436420AG_contract[845314].pdf</t>
         </is>
       </c>
       <c r="U38" s="4">
-        <v>294625</v>
+        <v>546436</v>
       </c>
       <c r="V38" s="8">
-        <v>3787.55</v>
+        <v>7000</v>
       </c>
       <c r="W38" s="8"/>
       <c r="X38" s="4"/>
       <c r="Y38" s="4">
-        <v>0.7</v>
+        <v>10.9</v>
       </c>
       <c r="Z38" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">📐 Spec Sheet</t>
         </is>
       </c>
-      <c r="AA38" s="4"/>
+      <c r="AA38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">We have marinated meats</t>
+        </is>
+      </c>
       <c r="AB38" s="4"/>
       <c r="AC38" s="6"/>
-      <c r="AD38" s="4"/>
+      <c r="AD38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cowboys: Dak</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7166O</t>
+          <t xml:space="preserve">2_7859O</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -4040,58 +4040,62 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G39" s="5"/>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">513964</t>
+        </is>
+      </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LBJ (635) .2Mi W/O Plano Road N/S F/E</t>
+          <t xml:space="preserve">I-35E 285' N/O Highland Village Road E/S F/S **Flagman Unit - No Sharp Installs / Take-Downs**</t>
         </is>
       </c>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="11">
-        <v>32.888565</v>
+        <v>33.08206</v>
       </c>
       <c r="L39" s="11">
-        <v>-96.704219</v>
+        <v>-97.025532</v>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14'' x 48"'</t>
         </is>
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">635 HV</t>
+          <t xml:space="preserve">I-35 HV</t>
         </is>
       </c>
       <c r="R39" s="7">
-        <v>46181</v>
+        <v>46216</v>
       </c>
       <c r="S39" s="7">
-        <v>46544</v>
+        <v>46579</v>
       </c>
       <c r="T39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4436420AG_contract[845314].pdf</t>
+          <t xml:space="preserve">1248526-SAT-HEB SAT 2026-01-22 15_10 CST.pdf</t>
         </is>
       </c>
       <c r="U39" s="5">
-        <v>546436</v>
+        <v>503687</v>
       </c>
       <c r="V39" s="9">
-        <v>7000</v>
+        <v>4050</v>
       </c>
       <c r="W39" s="9"/>
       <c r="X39" s="5"/>
       <c r="Y39" s="5">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="Z39" s="13" t="inlineStr">
         <is>
@@ -4107,14 +4111,14 @@
       <c r="AC39" s="7"/>
       <c r="AD39" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7859O</t>
+          <t xml:space="preserve">2_7891O</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -4144,25 +4148,25 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">513964</t>
+          <t xml:space="preserve">513983</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35E 285' N/O Highland Village Road E/S F/S **Flagman Unit - No Sharp Installs / Take-Downs**</t>
+          <t xml:space="preserve">I-35W S/O Loop 820 W/S F/N</t>
         </is>
       </c>
       <c r="I40" s="4"/>
       <c r="J40" s="4"/>
       <c r="K40" s="10">
-        <v>33.08206</v>
+        <v>32.8346</v>
       </c>
       <c r="L40" s="10">
-        <v>-97.025532</v>
+        <v>-97.313605</v>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N40" s="4"/>
@@ -4174,14 +4178,14 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35 HV</t>
+          <t xml:space="preserve">I-35W HV</t>
         </is>
       </c>
       <c r="R40" s="6">
-        <v>46216</v>
+        <v>46349</v>
       </c>
       <c r="S40" s="6">
-        <v>46579</v>
+        <v>46712</v>
       </c>
       <c r="T40" s="4" t="inlineStr">
         <is>
@@ -4189,15 +4193,15 @@
         </is>
       </c>
       <c r="U40" s="4">
-        <v>503687</v>
+        <v>441111</v>
       </c>
       <c r="V40" s="8">
-        <v>4050</v>
+        <v>5850</v>
       </c>
       <c r="W40" s="8"/>
       <c r="X40" s="4"/>
       <c r="Y40" s="4">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="Z40" s="12" t="inlineStr">
         <is>
@@ -4206,21 +4210,21 @@
       </c>
       <c r="AA40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">We have marinated meats</t>
+          <t xml:space="preserve">N/A</t>
         </is>
       </c>
       <c r="AB40" s="4"/>
       <c r="AC40" s="6"/>
       <c r="AD40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7891O</t>
+          <t xml:space="preserve">2_7904O</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -4248,62 +4252,58 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">513983</t>
-        </is>
-      </c>
+      <c r="G41" s="5"/>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35W S/O Loop 820 W/S F/N</t>
+          <t xml:space="preserve">3.7Mi N/O Mockingbird Lane E/S F/S</t>
         </is>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5"/>
       <c r="K41" s="11">
-        <v>32.8346</v>
+        <v>32.824007</v>
       </c>
       <c r="L41" s="11">
-        <v>-97.313605</v>
+        <v>-96.879435</v>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48"'</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P41" s="5"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35W HV</t>
+          <t xml:space="preserve">TX-183W HV</t>
         </is>
       </c>
       <c r="R41" s="7">
-        <v>46349</v>
+        <v>46216</v>
       </c>
       <c r="S41" s="7">
-        <v>46712</v>
+        <v>46579</v>
       </c>
       <c r="T41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248526-SAT-HEB SAT 2026-01-22 15_10 CST.pdf</t>
+          <t xml:space="preserve">4436420AG_contract[845314].pdf</t>
         </is>
       </c>
       <c r="U41" s="5">
-        <v>441111</v>
+        <v>585813</v>
       </c>
       <c r="V41" s="9">
-        <v>5850</v>
+        <v>5500</v>
       </c>
       <c r="W41" s="9"/>
       <c r="X41" s="5"/>
       <c r="Y41" s="5">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z41" s="13" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="AA41" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">Lives Up to the Buzz</t>
         </is>
       </c>
       <c r="AB41" s="5"/>
@@ -4326,7 +4326,7 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7904O</t>
+          <t xml:space="preserve">2_7953O</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
@@ -4354,58 +4354,62 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G42" s="4"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">514012</t>
+        </is>
+      </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.7Mi N/O Mockingbird Lane E/S F/S</t>
+          <t xml:space="preserve">LBJ (635) .5 Mi W/O Hillcrest S/S F/W</t>
         </is>
       </c>
       <c r="I42" s="4"/>
       <c r="J42" s="4"/>
       <c r="K42" s="10">
-        <v>32.824007</v>
+        <v>32.924224</v>
       </c>
       <c r="L42" s="10">
-        <v>-96.879435</v>
+        <v>-96.793911</v>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N42" s="4"/>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">14'' x 48"'</t>
         </is>
       </c>
       <c r="P42" s="4"/>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX-183W HV</t>
+          <t xml:space="preserve">635 HV</t>
         </is>
       </c>
       <c r="R42" s="6">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="S42" s="6">
-        <v>46579</v>
+        <v>46530</v>
       </c>
       <c r="T42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4436420AG_contract[845314].pdf</t>
+          <t xml:space="preserve">1248526-SAT-HEB SAT 2026-01-22 15_10 CST.pdf</t>
         </is>
       </c>
       <c r="U42" s="4">
-        <v>585813</v>
+        <v>1378437</v>
       </c>
       <c r="V42" s="8">
-        <v>5500</v>
+        <v>12600</v>
       </c>
       <c r="W42" s="8"/>
       <c r="X42" s="4"/>
       <c r="Y42" s="4">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="Z42" s="12" t="inlineStr">
         <is>
@@ -4414,7 +4418,7 @@
       </c>
       <c r="AA42" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lives Up to the Buzz</t>
+          <t xml:space="preserve">See what all the guac is about</t>
         </is>
       </c>
       <c r="AB42" s="4"/>
@@ -4428,7 +4432,7 @@
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7953O</t>
+          <t xml:space="preserve">2_7954O</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
@@ -4456,62 +4460,58 @@
           <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">514012</t>
-        </is>
-      </c>
+      <c r="G43" s="5"/>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">LBJ (635) .5 Mi W/O Hillcrest S/S F/W</t>
+          <t xml:space="preserve">Dallas North Tollway S/O Beltline E/S F/S</t>
         </is>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="11">
-        <v>32.924224</v>
+        <v>32.946604</v>
       </c>
       <c r="L43" s="11">
-        <v>-96.793911</v>
+        <v>-96.82291</v>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48"'</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P43" s="5"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">635 HV</t>
+          <t xml:space="preserve">Tollway HV</t>
         </is>
       </c>
       <c r="R43" s="7">
-        <v>46209</v>
+        <v>46181</v>
       </c>
       <c r="S43" s="7">
-        <v>46530</v>
+        <v>46544</v>
       </c>
       <c r="T43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248526-SAT-HEB SAT 2026-01-22 15_10 CST.pdf</t>
+          <t xml:space="preserve">4436420AG_contract[845314].pdf</t>
         </is>
       </c>
       <c r="U43" s="5">
-        <v>1378437</v>
+        <v>639308</v>
       </c>
       <c r="V43" s="9">
-        <v>12600</v>
+        <v>19500</v>
       </c>
       <c r="W43" s="9"/>
       <c r="X43" s="5"/>
       <c r="Y43" s="5">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="Z43" s="13" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="AA43" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">See what all the guac is about</t>
+          <t xml:space="preserve">We have marinated meats</t>
         </is>
       </c>
       <c r="AB43" s="5"/>
@@ -4534,7 +4534,7 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7954O</t>
+          <t xml:space="preserve">2_7956O</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
@@ -4565,16 +4565,16 @@
       <c r="G44" s="4"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dallas North Tollway S/O Beltline E/S F/S</t>
+          <t xml:space="preserve">Central (75) S/O LBJ Frwy E/S F/S</t>
         </is>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
       <c r="K44" s="10">
-        <v>32.946604</v>
+        <v>32.919253</v>
       </c>
       <c r="L44" s="10">
-        <v>-96.82291</v>
+        <v>-96.765381</v>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tollway HV</t>
+          <t xml:space="preserve">HWY 75 HV</t>
         </is>
       </c>
       <c r="R44" s="6">
@@ -4605,15 +4605,15 @@
         </is>
       </c>
       <c r="U44" s="4">
-        <v>639308</v>
+        <v>911767</v>
       </c>
       <c r="V44" s="8">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="W44" s="8"/>
       <c r="X44" s="4"/>
       <c r="Y44" s="4">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="Z44" s="12" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AA44" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">We have marinated meats</t>
+          <t xml:space="preserve">Psst... we have brisket queso</t>
         </is>
       </c>
       <c r="AB44" s="4"/>
@@ -4636,7 +4636,7 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_7956O</t>
+          <t xml:space="preserve">2_8098O</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
@@ -4667,20 +4667,20 @@
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Central (75) S/O LBJ Frwy E/S F/S</t>
+          <t xml:space="preserve">I-30 (E.R.L.T.) W/O Haskell S/S F/W</t>
         </is>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="11">
-        <v>32.919253</v>
+        <v>32.786233</v>
       </c>
       <c r="L45" s="11">
-        <v>-96.765381</v>
+        <v>-96.766122</v>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N45" s="5"/>
@@ -4692,7 +4692,7 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HWY 75 HV</t>
+          <t xml:space="preserve">I-30 Near DT HV</t>
         </is>
       </c>
       <c r="R45" s="7">
@@ -4707,15 +4707,15 @@
         </is>
       </c>
       <c r="U45" s="5">
-        <v>911767</v>
+        <v>540280</v>
       </c>
       <c r="V45" s="9">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="W45" s="9"/>
       <c r="X45" s="5"/>
       <c r="Y45" s="5">
-        <v>7.8</v>
+        <v>14.8</v>
       </c>
       <c r="Z45" s="13" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_8098O</t>
+          <t xml:space="preserve">2_8319O</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -4769,20 +4769,20 @@
       <c r="G46" s="4"/>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-30 (E.R.L.T.) W/O Haskell S/S F/W</t>
+          <t xml:space="preserve">I-35E .7Mi N/O Trinity Mills W/S F/N</t>
         </is>
       </c>
       <c r="I46" s="4"/>
       <c r="J46" s="4"/>
       <c r="K46" s="10">
-        <v>32.786233</v>
+        <v>32.987418</v>
       </c>
       <c r="L46" s="10">
-        <v>-96.766122</v>
+        <v>-96.938842</v>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N46" s="4"/>
@@ -4794,14 +4794,14 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-30 Near DT HV</t>
+          <t xml:space="preserve">I-35E HV</t>
         </is>
       </c>
       <c r="R46" s="6">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="S46" s="6">
-        <v>46544</v>
+        <v>46558</v>
       </c>
       <c r="T46" s="4" t="inlineStr">
         <is>
@@ -4809,15 +4809,15 @@
         </is>
       </c>
       <c r="U46" s="4">
-        <v>540280</v>
+        <v>736122</v>
       </c>
       <c r="V46" s="8">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="W46" s="8"/>
       <c r="X46" s="4"/>
       <c r="Y46" s="4">
-        <v>14.8</v>
+        <v>4.5</v>
       </c>
       <c r="Z46" s="12" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="AA46" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psst... we have brisket queso</t>
+          <t xml:space="preserve">We have marinated meats</t>
         </is>
       </c>
       <c r="AB46" s="4"/>
@@ -4840,7 +4840,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_8319O</t>
+          <t xml:space="preserve">2_8432O</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
@@ -4871,20 +4871,20 @@
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35E .7Mi N/O Trinity Mills W/S F/N</t>
+          <t xml:space="preserve">D.N. Tollway S/O Lovers Lane W/S F/S</t>
         </is>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="11">
-        <v>32.987418</v>
+        <v>32.850729</v>
       </c>
       <c r="L47" s="11">
-        <v>-96.938842</v>
+        <v>-96.813797</v>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N47" s="5"/>
@@ -4896,14 +4896,14 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35E HV</t>
+          <t xml:space="preserve">Tollway HV</t>
         </is>
       </c>
       <c r="R47" s="7">
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="S47" s="7">
-        <v>46558</v>
+        <v>46586</v>
       </c>
       <c r="T47" s="5" t="inlineStr">
         <is>
@@ -4911,15 +4911,15 @@
         </is>
       </c>
       <c r="U47" s="5">
-        <v>736122</v>
+        <v>442450</v>
       </c>
       <c r="V47" s="9">
-        <v>4000</v>
+        <v>18000</v>
       </c>
       <c r="W47" s="9"/>
       <c r="X47" s="5"/>
       <c r="Y47" s="5">
-        <v>4.5</v>
+        <v>9.9</v>
       </c>
       <c r="Z47" s="13" t="inlineStr">
         <is>
@@ -4928,21 +4928,21 @@
       </c>
       <c r="AA47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">We have marinated meats</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB47" s="5"/>
       <c r="AC47" s="7"/>
       <c r="AD47" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2_8432O</t>
+          <t xml:space="preserve">3_3009O</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -4973,16 +4973,16 @@
       <c r="G48" s="4"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D.N. Tollway S/O Lovers Lane W/S F/S</t>
+          <t xml:space="preserve">Central (75) 1000' N/O Parker Road W/S F/S</t>
         </is>
       </c>
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="10">
-        <v>32.850729</v>
+        <v>33.053851</v>
       </c>
       <c r="L48" s="10">
-        <v>-96.813797</v>
+        <v>-96.696414</v>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
@@ -4992,20 +4992,20 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">10'' x 30''</t>
         </is>
       </c>
       <c r="P48" s="4"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tollway HV</t>
+          <t xml:space="preserve">HWY 75 HV</t>
         </is>
       </c>
       <c r="R48" s="6">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="S48" s="6">
-        <v>46586</v>
+        <v>46607</v>
       </c>
       <c r="T48" s="4" t="inlineStr">
         <is>
@@ -5013,15 +5013,15 @@
         </is>
       </c>
       <c r="U48" s="4">
-        <v>442450</v>
+        <v>444000</v>
       </c>
       <c r="V48" s="8">
-        <v>18000</v>
+        <v>6500</v>
       </c>
       <c r="W48" s="8"/>
       <c r="X48" s="4"/>
       <c r="Y48" s="4">
-        <v>9.9</v>
+        <v>4.9</v>
       </c>
       <c r="Z48" s="12" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AA48" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">Pound for Pound</t>
         </is>
       </c>
       <c r="AB48" s="4"/>
@@ -5044,7 +5044,7 @@
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">3_3009O</t>
+          <t xml:space="preserve">4_7860O</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
@@ -5075,39 +5075,39 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Central (75) 1000' N/O Parker Road W/S F/S</t>
+          <t xml:space="preserve">Hwy 80 1.50mi E/O Beltline N/S F/E</t>
         </is>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5"/>
       <c r="K49" s="11">
-        <v>33.053851</v>
+        <v>32.787755</v>
       </c>
       <c r="L49" s="11">
-        <v>-96.696414</v>
+        <v>-96.57554</v>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">East</t>
         </is>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10'' x 30''</t>
+          <t xml:space="preserve">10'' x 40''</t>
         </is>
       </c>
       <c r="P49" s="5"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">HWY 75 HV</t>
+          <t xml:space="preserve">US-80 HV</t>
         </is>
       </c>
       <c r="R49" s="7">
-        <v>46244</v>
+        <v>46195</v>
       </c>
       <c r="S49" s="7">
-        <v>46607</v>
+        <v>46558</v>
       </c>
       <c r="T49" s="5" t="inlineStr">
         <is>
@@ -5115,15 +5115,15 @@
         </is>
       </c>
       <c r="U49" s="5">
-        <v>444000</v>
+        <v>289424</v>
       </c>
       <c r="V49" s="9">
-        <v>6500</v>
+        <v>2500</v>
       </c>
       <c r="W49" s="9"/>
       <c r="X49" s="5"/>
       <c r="Y49" s="5">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="Z49" s="13" t="inlineStr">
         <is>
@@ -5132,21 +5132,21 @@
       </c>
       <c r="AA49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB49" s="5"/>
       <c r="AC49" s="7"/>
       <c r="AD49" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4_7860O</t>
+          <t xml:space="preserve">4_8541O</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -5177,20 +5177,20 @@
       <c r="G50" s="4"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy 80 1.50mi E/O Beltline N/S F/E</t>
+          <t xml:space="preserve">Preston .25Mi S/O Old Shephard Road E/S F/S</t>
         </is>
       </c>
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="10">
-        <v>32.787755</v>
+        <v>33.01974</v>
       </c>
       <c r="L50" s="10">
-        <v>-96.57554</v>
+        <v>-96.794792</v>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N50" s="4"/>
@@ -5202,14 +5202,14 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">US-80 HV</t>
+          <t xml:space="preserve">Preston Rd. HV</t>
         </is>
       </c>
       <c r="R50" s="6">
-        <v>46195</v>
+        <v>46244</v>
       </c>
       <c r="S50" s="6">
-        <v>46558</v>
+        <v>46607</v>
       </c>
       <c r="T50" s="4" t="inlineStr">
         <is>
@@ -5217,15 +5217,15 @@
         </is>
       </c>
       <c r="U50" s="4">
-        <v>289424</v>
+        <v>291803</v>
       </c>
       <c r="V50" s="8">
-        <v>2500</v>
+        <v>4000</v>
       </c>
       <c r="W50" s="8"/>
       <c r="X50" s="4"/>
       <c r="Y50" s="4">
-        <v>8</v>
+        <v>0.8</v>
       </c>
       <c r="Z50" s="12" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="AA50" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">We have marinated meats</t>
         </is>
       </c>
       <c r="AB50" s="4"/>
@@ -5248,22 +5248,22 @@
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4_8541O</t>
+          <t xml:space="preserve">133A</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outfront Media</t>
+          <t xml:space="preserve">Primary Media</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sammy Tamporello</t>
+          <t xml:space="preserve">Jeremy Wright</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sammy.tamporello@outfront.com</t>
+          <t xml:space="preserve">jeremy@primarymedia.com</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -5273,61 +5273,73 @@
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preston .25Mi S/O Old Shephard Road E/S F/S</t>
-        </is>
-      </c>
-      <c r="I51" s="5"/>
-      <c r="J51" s="5"/>
+          <t xml:space="preserve">WB/RHR US 380 @ Hardin Blvd (adjacent Costco &amp; 380 Crossing)</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">McKinney</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75070</t>
+        </is>
+      </c>
       <c r="K51" s="11">
-        <v>33.01974</v>
+        <v>33.2177</v>
       </c>
       <c r="L51" s="11">
-        <v>-96.794792</v>
+        <v>-96.66436</v>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N51" s="5"/>
+          <t xml:space="preserve">East</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10'' x 40''</t>
+          <t xml:space="preserve">10' x 30'</t>
         </is>
       </c>
       <c r="P51" s="5"/>
-      <c r="Q51" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preston Rd. HV</t>
-        </is>
-      </c>
+      <c r="Q51" s="5"/>
       <c r="R51" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="S51" s="7">
-        <v>46607</v>
+        <v>46320</v>
       </c>
       <c r="T51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4436420AG_contract[845314].pdf</t>
+          <t xml:space="preserve">SignedContracts_P559305_7_23_2026_191938.pdf</t>
         </is>
       </c>
       <c r="U51" s="5">
-        <v>291803</v>
+        <v>1349696</v>
       </c>
       <c r="V51" s="9">
-        <v>4000</v>
+        <v>3650</v>
       </c>
       <c r="W51" s="9"/>
-      <c r="X51" s="5"/>
+      <c r="X51" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📷 Panel Photo</t>
+        </is>
+      </c>
       <c r="Y51" s="5">
-        <v>0.8</v>
+        <v>4.6</v>
       </c>
       <c r="Z51" s="13" t="inlineStr">
         <is>
@@ -5336,10 +5348,14 @@
       </c>
       <c r="AA51" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">We have marinated meats</t>
-        </is>
-      </c>
-      <c r="AB51" s="5"/>
+          <t xml:space="preserve">Pound for Pound</t>
+        </is>
+      </c>
+      <c r="AB51" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AEM link in Airtable — copy from Airtable record</t>
+        </is>
+      </c>
       <c r="AC51" s="7"/>
       <c r="AD51" s="5" t="inlineStr">
         <is>
@@ -5350,7 +5366,7 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">133A</t>
+          <t xml:space="preserve">800A</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -5381,28 +5397,24 @@
       <c r="G52" s="4"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">WB/RHR US 380 @ Hardin Blvd (adjacent Costco &amp; 380 Crossing)</t>
+          <t xml:space="preserve">US 380 at Coit Rd — "front door of McKinney"</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">McKinney</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75070</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Frisco</t>
+        </is>
+      </c>
+      <c r="J52" s="4"/>
       <c r="K52" s="10">
-        <v>33.2177</v>
+        <v>33.21793</v>
       </c>
       <c r="L52" s="10">
-        <v>-96.66436</v>
+        <v>-96.76865</v>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">East</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -5412,7 +5424,7 @@
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' x 30'</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P52" s="4"/>
@@ -5429,10 +5441,10 @@
         </is>
       </c>
       <c r="U52" s="4">
-        <v>1349696</v>
+        <v>760443</v>
       </c>
       <c r="V52" s="8">
-        <v>3650</v>
+        <v>4650</v>
       </c>
       <c r="W52" s="8"/>
       <c r="X52" s="12" t="inlineStr">
@@ -5441,7 +5453,7 @@
         </is>
       </c>
       <c r="Y52" s="4">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="Z52" s="12" t="inlineStr">
         <is>
@@ -5450,7 +5462,7 @@
       </c>
       <c r="AA52" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">See what all the guac is about</t>
         </is>
       </c>
       <c r="AB52" s="4" t="inlineStr">
@@ -5468,22 +5480,18 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">800A</t>
+          <t xml:space="preserve">Choctaw Stadium</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Primary Media</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jeremy Wright</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Rev Entertainment</t>
+        </is>
+      </c>
+      <c r="C53" s="5"/>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">jeremy@primarymedia.com</t>
+          <t xml:space="preserve">krhodes@reventertainment.com</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -5493,107 +5501,77 @@
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Choctaw Stadium</t>
         </is>
       </c>
       <c r="G53" s="5"/>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">US 380 at Coit Rd — "front door of McKinney"</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Frisco</t>
-        </is>
-      </c>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
       <c r="J53" s="5"/>
       <c r="K53" s="11">
-        <v>33.21793</v>
+        <v>32.75101</v>
       </c>
       <c r="L53" s="11">
-        <v>-96.76865</v>
-      </c>
-      <c r="M53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14' x 48'</t>
-        </is>
-      </c>
+        <v>-97.08299</v>
+      </c>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
       <c r="P53" s="5"/>
-      <c r="Q53" s="5"/>
+      <c r="Q53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HV</t>
+        </is>
+      </c>
       <c r="R53" s="7">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="S53" s="7">
-        <v>46320</v>
-      </c>
-      <c r="T53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SignedContracts_P559305_7_23_2026_191938.pdf</t>
-        </is>
-      </c>
-      <c r="U53" s="5">
-        <v>760443</v>
-      </c>
+        <v>46313</v>
+      </c>
+      <c r="T53" s="5"/>
+      <c r="U53" s="5"/>
       <c r="V53" s="9">
-        <v>4650</v>
+        <v>175000</v>
       </c>
       <c r="W53" s="9"/>
-      <c r="X53" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📷 Panel Photo</t>
-        </is>
-      </c>
+      <c r="X53" s="5"/>
       <c r="Y53" s="5">
-        <v>3.1</v>
-      </c>
-      <c r="Z53" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
+        <v>8.1</v>
+      </c>
+      <c r="Z53" s="5"/>
       <c r="AA53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">See what all the guac is about</t>
-        </is>
-      </c>
-      <c r="AB53" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AEM link in Airtable — copy from Airtable record</t>
-        </is>
-      </c>
+          <t xml:space="preserve">N/A</t>
+        </is>
+      </c>
+      <c r="AB53" s="5"/>
       <c r="AC53" s="7"/>
       <c r="AD53" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choctaw Stadium</t>
+          <t xml:space="preserve">003-009L</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rev Entertainment</t>
-        </is>
-      </c>
-      <c r="C54" s="4"/>
+          <t xml:space="preserve">The Reiss Group</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisa</t>
+        </is>
+      </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">krhodes@reventertainment.com</t>
+          <t xml:space="preserve">Lisa@thereissgroup.net</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -5603,62 +5581,100 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Choctaw Stadium</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6108 South US Highway 75 South — US 75 SB, 1.5 mi. S of 121 Toll at Boy Scout Council</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fairview</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75069</t>
+        </is>
+      </c>
       <c r="K54" s="10">
-        <v>32.75101</v>
+        <v>33.137</v>
       </c>
       <c r="L54" s="10">
-        <v>-97.08299</v>
-      </c>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HV</t>
-        </is>
-      </c>
+        <v>-96.652</v>
+      </c>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Left</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14x48</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
+      <c r="Q54" s="4"/>
       <c r="R54" s="6">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="S54" s="6">
-        <v>46313</v>
+        <v>46327</v>
       </c>
       <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
+      <c r="U54" s="4">
+        <v>781200</v>
+      </c>
       <c r="V54" s="8">
-        <v>175000</v>
+        <v>5800</v>
       </c>
       <c r="W54" s="8"/>
-      <c r="X54" s="4"/>
+      <c r="X54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📷 Panel Photo</t>
+        </is>
+      </c>
       <c r="Y54" s="4">
-        <v>8.1</v>
-      </c>
-      <c r="Z54" s="4"/>
+        <v>1.5</v>
+      </c>
+      <c r="Z54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
       <c r="AA54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
-        </is>
-      </c>
-      <c r="AB54" s="4"/>
+          <t xml:space="preserve">Pound for Pound</t>
+        </is>
+      </c>
+      <c r="AB54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AEM link in Airtable — copy from Airtable record</t>
+        </is>
+      </c>
       <c r="AC54" s="6"/>
       <c r="AD54" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">003-009L</t>
+          <t xml:space="preserve">003-055L</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
@@ -5689,28 +5705,28 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6108 South US Highway 75 South — US 75 SB, 1.5 mi. S of 121 Toll at Boy Scout Council</t>
+          <t xml:space="preserve">26401 East University Drive — NE Corner of Hwy 380 EB &amp; FM 720</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fairview</t>
+          <t xml:space="preserve">Little Elm</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">75069</t>
+          <t xml:space="preserve">76227</t>
         </is>
       </c>
       <c r="K55" s="11">
-        <v>33.137</v>
+        <v>33.2240146</v>
       </c>
       <c r="L55" s="11">
-        <v>-96.652</v>
+        <v>-96.9759375</v>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N55" s="5" t="inlineStr">
@@ -5720,7 +5736,7 @@
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14x48</t>
+          <t xml:space="preserve">14' x 48'</t>
         </is>
       </c>
       <c r="P55" s="5" t="inlineStr">
@@ -5733,14 +5749,14 @@
         <v>46244</v>
       </c>
       <c r="S55" s="7">
-        <v>46327</v>
+        <v>46383</v>
       </c>
       <c r="T55" s="5"/>
       <c r="U55" s="5">
-        <v>781200</v>
+        <v>217000</v>
       </c>
       <c r="V55" s="9">
-        <v>5800</v>
+        <v>2500</v>
       </c>
       <c r="W55" s="9"/>
       <c r="X55" s="13" t="inlineStr">
@@ -5749,7 +5765,7 @@
         </is>
       </c>
       <c r="Y55" s="5">
-        <v>1.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z55" s="13" t="inlineStr">
         <is>
@@ -5758,7 +5774,7 @@
       </c>
       <c r="AA55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB55" s="5" t="inlineStr">
@@ -5769,14 +5785,14 @@
       <c r="AC55" s="7"/>
       <c r="AD55" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">003-055L</t>
+          <t xml:space="preserve">003-056L</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -5807,7 +5823,7 @@
       <c r="G56" s="4"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">26401 East University Drive — NE Corner of Hwy 380 EB &amp; FM 720</t>
+          <t xml:space="preserve">4201 Carnelian Road — Hwy.380 EB,2/10 mile east of FM 720</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -5821,10 +5837,10 @@
         </is>
       </c>
       <c r="K56" s="10">
-        <v>33.2240146</v>
+        <v>33.22362</v>
       </c>
       <c r="L56" s="10">
-        <v>-96.9759375</v>
+        <v>-96.973</v>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
@@ -5838,7 +5854,7 @@
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14' x 48'</t>
+          <t xml:space="preserve">14x48</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
@@ -5858,7 +5874,7 @@
         <v>217000</v>
       </c>
       <c r="V56" s="8">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="W56" s="8"/>
       <c r="X56" s="12" t="inlineStr">
@@ -5867,7 +5883,7 @@
         </is>
       </c>
       <c r="Y56" s="4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Z56" s="12" t="inlineStr">
         <is>
@@ -5876,7 +5892,7 @@
       </c>
       <c r="AA56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">Pound for Pound</t>
         </is>
       </c>
       <c r="AB56" s="4" t="inlineStr">
@@ -5887,14 +5903,14 @@
       <c r="AC56" s="6"/>
       <c r="AD56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
+          <t xml:space="preserve">Cowboys: Delivery</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">003-056L</t>
+          <t xml:space="preserve">003-057L</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
@@ -5925,7 +5941,7 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">4201 Carnelian Road — Hwy.380 EB,2/10 mile east of FM 720</t>
+          <t xml:space="preserve">4101 Hillstone Pointe Boulevard — Hwy.380 EB,.3/10 mi east of FM 720</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
@@ -5939,10 +5955,10 @@
         </is>
       </c>
       <c r="K57" s="11">
-        <v>33.22362</v>
+        <v>33.22337</v>
       </c>
       <c r="L57" s="11">
-        <v>-96.973</v>
+        <v>-96.9714</v>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
@@ -5985,7 +6001,7 @@
         </is>
       </c>
       <c r="Y57" s="5">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
       <c r="Z57" s="13" t="inlineStr">
         <is>
@@ -5994,7 +6010,7 @@
       </c>
       <c r="AA57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
+          <t xml:space="preserve">Psst... we have brisket queso</t>
         </is>
       </c>
       <c r="AB57" s="5" t="inlineStr">
@@ -6005,14 +6021,14 @@
       <c r="AC57" s="7"/>
       <c r="AD57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Delivery</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">003-057L</t>
+          <t xml:space="preserve">003-316RD-1</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -6037,44 +6053,44 @@
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital-Bulletin</t>
         </is>
       </c>
       <c r="G58" s="4"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">4101 Hillstone Pointe Boulevard — Hwy.380 EB,.3/10 mi east of FM 720</t>
+          <t xml:space="preserve">2698 North Central Expressway — US 75 NB at Wilmeth Rd Digital</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Little Elm</t>
+          <t xml:space="preserve">McKinney</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">76227</t>
+          <t xml:space="preserve">75070</t>
         </is>
       </c>
       <c r="K58" s="10">
-        <v>33.22337</v>
+        <v>33.2278</v>
       </c>
       <c r="L58" s="10">
-        <v>-96.9714</v>
+        <v>-96.6326</v>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Left</t>
+          <t xml:space="preserve">Right</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14x48</t>
+          <t xml:space="preserve">10x30</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
@@ -6087,14 +6103,14 @@
         <v>46244</v>
       </c>
       <c r="S58" s="6">
-        <v>46383</v>
+        <v>46327</v>
       </c>
       <c r="T58" s="4"/>
       <c r="U58" s="4">
-        <v>217000</v>
+        <v>421200</v>
       </c>
       <c r="V58" s="8">
-        <v>2400</v>
+        <v>2900</v>
       </c>
       <c r="W58" s="8"/>
       <c r="X58" s="12" t="inlineStr">
@@ -6103,7 +6119,7 @@
         </is>
       </c>
       <c r="Y58" s="4">
-        <v>8.3</v>
+        <v>3.6</v>
       </c>
       <c r="Z58" s="12" t="inlineStr">
         <is>
@@ -6112,25 +6128,25 @@
       </c>
       <c r="AA58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Psst... we have brisket queso</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">AEM link in Airtable — copy from Airtable record</t>
+          <t xml:space="preserve">NEEDS RESEND (per Airtable 8/4)</t>
         </is>
       </c>
       <c r="AC58" s="6"/>
       <c r="AD58" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: Delivery</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">003-316RD-1</t>
+          <t xml:space="preserve">003-390L</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
@@ -6138,11 +6154,7 @@
           <t xml:space="preserve">The Reiss Group</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisa</t>
-        </is>
-      </c>
+      <c r="C59" s="5"/>
       <c r="D59" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Lisa@thereissgroup.net</t>
@@ -6155,73 +6167,61 @@
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital-Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2698 North Central Expressway — US 75 NB at Wilmeth Rd Digital</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">McKinney</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">75070</t>
-        </is>
-      </c>
+          <t xml:space="preserve">NE Corner of Hwy 78 SB &amp; Ballard Ave.</t>
+        </is>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
       <c r="K59" s="11">
-        <v>33.2278</v>
+        <v>33.01173</v>
       </c>
       <c r="L59" s="11">
-        <v>-96.6326</v>
+        <v>-96.5395</v>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Right</t>
-        </is>
-      </c>
+          <t xml:space="preserve">North</t>
+        </is>
+      </c>
+      <c r="N59" s="5"/>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10x30</t>
-        </is>
-      </c>
-      <c r="P59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q59" s="5"/>
+          <t xml:space="preserve">16' x 32'</t>
+        </is>
+      </c>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HWY 78 HV</t>
+        </is>
+      </c>
       <c r="R59" s="7">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="S59" s="7">
-        <v>46327</v>
-      </c>
-      <c r="T59" s="5"/>
+        <v>46530</v>
+      </c>
+      <c r="T59" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEB Renewals RG_merged cosigned.pdf</t>
+        </is>
+      </c>
       <c r="U59" s="5">
-        <v>421200</v>
+        <v>195300</v>
       </c>
       <c r="V59" s="9">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="W59" s="9"/>
-      <c r="X59" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📷 Panel Photo</t>
-        </is>
-      </c>
+      <c r="X59" s="5"/>
       <c r="Y59" s="5">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="Z59" s="13" t="inlineStr">
         <is>
@@ -6230,25 +6230,21 @@
       </c>
       <c r="AA59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
-      <c r="AB59" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NEEDS RESEND (per Airtable 8/4)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">GO: Now Open</t>
+        </is>
+      </c>
+      <c r="AB59" s="5"/>
       <c r="AC59" s="7"/>
       <c r="AD59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Delivery</t>
+          <t xml:space="preserve">Cowboys: Dak</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">003-390L</t>
+          <t xml:space="preserve">006-78074</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -6269,84 +6265,68 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G60" s="4"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NE Corner of Hwy 78 SB &amp; Ballard Ave.</t>
+          <t xml:space="preserve">I-35W WS 0.4mi S/O FM 407, Corral City, Denton County, TX</t>
         </is>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
       <c r="K60" s="10">
-        <v>33.01173</v>
+        <v>33.09475</v>
       </c>
       <c r="L60" s="10">
-        <v>-96.5395</v>
+        <v>-97.227977</v>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N60" s="4"/>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">16' x 32'</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P60" s="4"/>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HWY 78 HV</t>
-        </is>
-      </c>
+      <c r="Q60" s="4"/>
       <c r="R60" s="6">
-        <v>46209</v>
+        <v>46328</v>
       </c>
       <c r="S60" s="6">
-        <v>46530</v>
+        <v>46397</v>
       </c>
       <c r="T60" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEB Renewals RG_merged cosigned.pdf</t>
+          <t xml:space="preserve">Robson Ranch_GD.pdf</t>
         </is>
       </c>
       <c r="U60" s="4">
-        <v>195300</v>
+        <v>95992</v>
       </c>
       <c r="V60" s="8">
-        <v>2500</v>
+        <v>2400</v>
       </c>
       <c r="W60" s="8"/>
       <c r="X60" s="4"/>
       <c r="Y60" s="4">
-        <v>0.6</v>
-      </c>
-      <c r="Z60" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
-      <c r="AA60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GO: Now Open</t>
-        </is>
-      </c>
+        <v>2.6</v>
+      </c>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
       <c r="AB60" s="4"/>
       <c r="AC60" s="6"/>
-      <c r="AD60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
-        </is>
-      </c>
+      <c r="AD60" s="4"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">006-78074</t>
+          <t xml:space="preserve">006-78728</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
@@ -6373,20 +6353,20 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35W WS 0.4mi S/O FM 407, Corral City, Denton County, TX</t>
+          <t xml:space="preserve">I-35W WS 500ft S/O FM 407 F/S - 1, Corral City, Denton County, TX</t>
         </is>
       </c>
       <c r="I61" s="5"/>
       <c r="J61" s="5"/>
       <c r="K61" s="11">
-        <v>33.09475</v>
+        <v>33.098967</v>
       </c>
       <c r="L61" s="11">
-        <v>-97.227977</v>
+        <v>-97.226056</v>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N61" s="5"/>
@@ -6409,7 +6389,7 @@
         </is>
       </c>
       <c r="U61" s="5">
-        <v>95992</v>
+        <v>63570</v>
       </c>
       <c r="V61" s="9">
         <v>2400</v>
@@ -6417,7 +6397,7 @@
       <c r="W61" s="9"/>
       <c r="X61" s="5"/>
       <c r="Y61" s="5">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="Z61" s="5"/>
       <c r="AA61" s="5"/>
@@ -6428,7 +6408,7 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">006-78728</t>
+          <t xml:space="preserve">008-0507A</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -6436,7 +6416,11 @@
           <t xml:space="preserve">The Reiss Group</t>
         </is>
       </c>
-      <c r="C62" s="4"/>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lisa</t>
+        </is>
+      </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Lisa@thereissgroup.net</t>
@@ -6449,68 +6433,100 @@
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G62" s="4"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35W WS 500ft S/O FM 407 F/S - 1, Corral City, Denton County, TX</t>
-        </is>
-      </c>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
+          <t xml:space="preserve">6428 K Avenue — US 75 NB, 3/10 mi. N. of Spring Creek Pkwy</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plano</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">75074</t>
+        </is>
+      </c>
       <c r="K62" s="10">
-        <v>33.098967</v>
+        <v>33.061762</v>
       </c>
       <c r="L62" s="10">
-        <v>-97.226056</v>
+        <v>-96.6911</v>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">South</t>
         </is>
       </c>
-      <c r="N62" s="4"/>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Right</t>
+        </is>
+      </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
-        </is>
-      </c>
-      <c r="P62" s="4"/>
+          <t xml:space="preserve">10x30</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Y</t>
+        </is>
+      </c>
       <c r="Q62" s="4"/>
       <c r="R62" s="6">
-        <v>46328</v>
+        <v>46244</v>
       </c>
       <c r="S62" s="6">
-        <v>46397</v>
-      </c>
-      <c r="T62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Robson Ranch_GD.pdf</t>
-        </is>
-      </c>
+        <v>46327</v>
+      </c>
+      <c r="T62" s="4"/>
       <c r="U62" s="4">
-        <v>63570</v>
+        <v>421200</v>
       </c>
       <c r="V62" s="8">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="W62" s="8"/>
-      <c r="X62" s="4"/>
+      <c r="X62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📷 Panel Photo</t>
+        </is>
+      </c>
       <c r="Y62" s="4">
-        <v>2.3</v>
-      </c>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
-      <c r="AB62" s="4"/>
+        <v>4.3</v>
+      </c>
+      <c r="Z62" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
+      <c r="AA62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
+      <c r="AB62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AEM link in Airtable — copy from Airtable record</t>
+        </is>
+      </c>
       <c r="AC62" s="6"/>
-      <c r="AD62" s="4"/>
+      <c r="AD62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cowboys: Dak</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">008-0507A</t>
+          <t xml:space="preserve">040-1212L</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
@@ -6541,24 +6557,24 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">6428 K Avenue — US 75 NB, 3/10 mi. N. of Spring Creek Pkwy</t>
+          <t xml:space="preserve">6503 North Freeway — I-35W NB at Western Center Blvd (west side of 35W)</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plano</t>
+          <t xml:space="preserve">Fort Worth</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">75074</t>
+          <t xml:space="preserve">76131</t>
         </is>
       </c>
       <c r="K63" s="11">
-        <v>33.061762</v>
+        <v>32.8596</v>
       </c>
       <c r="L63" s="11">
-        <v>-96.6911</v>
+        <v>-97.3146</v>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
@@ -6567,12 +6583,12 @@
       </c>
       <c r="N63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Right</t>
+          <t xml:space="preserve">Left</t>
         </is>
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">10x30</t>
+          <t xml:space="preserve">14x48</t>
         </is>
       </c>
       <c r="P63" s="5" t="inlineStr">
@@ -6589,10 +6605,10 @@
       </c>
       <c r="T63" s="5"/>
       <c r="U63" s="5">
-        <v>421200</v>
+        <v>263082</v>
       </c>
       <c r="V63" s="9">
-        <v>2500</v>
+        <v>5800</v>
       </c>
       <c r="W63" s="9"/>
       <c r="X63" s="13" t="inlineStr">
@@ -6601,7 +6617,7 @@
         </is>
       </c>
       <c r="Y63" s="5">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="Z63" s="13" t="inlineStr">
         <is>
@@ -6610,7 +6626,7 @@
       </c>
       <c r="AA63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">Pound for Pound</t>
         </is>
       </c>
       <c r="AB63" s="5" t="inlineStr">
@@ -6621,14 +6637,14 @@
       <c r="AC63" s="7"/>
       <c r="AD63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
+          <t xml:space="preserve">Cowboys: Delivery</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">040-1212L</t>
+          <t xml:space="preserve">058L</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -6636,11 +6652,7 @@
           <t xml:space="preserve">The Reiss Group</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisa</t>
-        </is>
-      </c>
+      <c r="C64" s="4"/>
       <c r="D64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Lisa@thereissgroup.net</t>
@@ -6659,67 +6671,55 @@
       <c r="G64" s="4"/>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6503 North Freeway — I-35W NB at Western Center Blvd (west side of 35W)</t>
-        </is>
-      </c>
-      <c r="I64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fort Worth</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76131</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Hwy.380 EB, 1/10 mi east of FM 720</t>
+        </is>
+      </c>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
       <c r="K64" s="10">
-        <v>32.8596</v>
+        <v>33.2238306</v>
       </c>
       <c r="L64" s="10">
-        <v>-97.3146</v>
+        <v>-96.9745374</v>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
-        </is>
-      </c>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Left</t>
-        </is>
-      </c>
+          <t xml:space="preserve">West</t>
+        </is>
+      </c>
+      <c r="N64" s="4"/>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">14x48</t>
-        </is>
-      </c>
-      <c r="P64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Y</t>
-        </is>
-      </c>
-      <c r="Q64" s="4"/>
+          <t xml:space="preserve">14'' x 48''</t>
+        </is>
+      </c>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183 HV</t>
+        </is>
+      </c>
       <c r="R64" s="6">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="S64" s="6">
-        <v>46327</v>
-      </c>
-      <c r="T64" s="4"/>
+        <v>46383</v>
+      </c>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEB Renewals RG_merged cosigned.pdf</t>
+        </is>
+      </c>
       <c r="U64" s="4">
-        <v>263082</v>
+        <v>217000</v>
       </c>
       <c r="V64" s="8">
-        <v>5800</v>
+        <v>2300</v>
       </c>
       <c r="W64" s="8"/>
-      <c r="X64" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📷 Panel Photo</t>
-        </is>
-      </c>
+      <c r="X64" s="4"/>
       <c r="Y64" s="4">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="Z64" s="12" t="inlineStr">
         <is>
@@ -6728,25 +6728,21 @@
       </c>
       <c r="AA64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pound for Pound</t>
-        </is>
-      </c>
-      <c r="AB64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">AEM link in Airtable — copy from Airtable record</t>
-        </is>
-      </c>
+          <t xml:space="preserve">We have marinated meats</t>
+        </is>
+      </c>
+      <c r="AB64" s="4"/>
       <c r="AC64" s="6"/>
       <c r="AD64" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys: Delivery</t>
+          <t xml:space="preserve">Cowboys Fan</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">058L</t>
+          <t xml:space="preserve">1240R</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
@@ -6773,32 +6769,32 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hwy.380 EB, 1/10 mi east of FM 720</t>
+          <t xml:space="preserve">Preston Rd. NB, just s/o Hwy 121</t>
         </is>
       </c>
       <c r="I65" s="5"/>
       <c r="J65" s="5"/>
       <c r="K65" s="11">
-        <v>33.2238306</v>
+        <v>33.091992</v>
       </c>
       <c r="L65" s="11">
-        <v>-96.9745374</v>
+        <v>-96.805388</v>
       </c>
       <c r="M65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">South</t>
         </is>
       </c>
       <c r="N65" s="5"/>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">12'' x 40''</t>
         </is>
       </c>
       <c r="P65" s="5"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">183 HV</t>
+          <t xml:space="preserve">Preston Rd. HV</t>
         </is>
       </c>
       <c r="R65" s="7">
@@ -6813,15 +6809,15 @@
         </is>
       </c>
       <c r="U65" s="5">
-        <v>217000</v>
+        <v>434000</v>
       </c>
       <c r="V65" s="9">
-        <v>2300</v>
+        <v>8600</v>
       </c>
       <c r="W65" s="9"/>
       <c r="X65" s="5"/>
       <c r="Y65" s="5">
-        <v>8.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z65" s="13" t="inlineStr">
         <is>
@@ -6830,21 +6826,21 @@
       </c>
       <c r="AA65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">We have marinated meats</t>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
         </is>
       </c>
       <c r="AB65" s="5"/>
       <c r="AC65" s="7"/>
       <c r="AD65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cowboys Fan</t>
+          <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240R</t>
+          <t xml:space="preserve">181-119</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
@@ -6865,84 +6861,68 @@
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bulletin</t>
+          <t xml:space="preserve">Digital Bulletin</t>
         </is>
       </c>
       <c r="G66" s="4"/>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preston Rd. NB, just s/o Hwy 121</t>
+          <t xml:space="preserve">I-35W W/L .5mi N/O FM 1171, Northlake, Denton County, TX</t>
         </is>
       </c>
       <c r="I66" s="4"/>
       <c r="J66" s="4"/>
       <c r="K66" s="10">
-        <v>33.091992</v>
+        <v>33.07169</v>
       </c>
       <c r="L66" s="10">
-        <v>-96.805388</v>
+        <v>-97.2405</v>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">South</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N66" s="4"/>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12'' x 40''</t>
+          <t xml:space="preserve">14'' x 48''</t>
         </is>
       </c>
       <c r="P66" s="4"/>
-      <c r="Q66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preston Rd. HV</t>
-        </is>
-      </c>
+      <c r="Q66" s="4"/>
       <c r="R66" s="6">
-        <v>46209</v>
+        <v>46328</v>
       </c>
       <c r="S66" s="6">
-        <v>46383</v>
+        <v>46397</v>
       </c>
       <c r="T66" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEB Renewals RG_merged cosigned.pdf</t>
+          <t xml:space="preserve">Robson Ranch_GD.pdf</t>
         </is>
       </c>
       <c r="U66" s="4">
-        <v>434000</v>
+        <v>120067</v>
       </c>
       <c r="V66" s="8">
-        <v>8600</v>
+        <v>3293</v>
       </c>
       <c r="W66" s="8"/>
       <c r="X66" s="4"/>
       <c r="Y66" s="4">
-        <v>4.4</v>
-      </c>
-      <c r="Z66" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
-      <c r="AA66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
-        </is>
-      </c>
+        <v>4.3</v>
+      </c>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
       <c r="AB66" s="4"/>
       <c r="AC66" s="6"/>
-      <c r="AD66" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cowboys: DeMo</t>
-        </is>
-      </c>
+      <c r="AD66" s="4"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">181-119</t>
+          <t xml:space="preserve">290R</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
@@ -6963,68 +6943,84 @@
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digital Bulletin</t>
+          <t xml:space="preserve">Bulletin</t>
         </is>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">I-35W W/L .5mi N/O FM 1171, Northlake, Denton County, TX</t>
+          <t xml:space="preserve">Preston Rd.SB @Celina Storage</t>
         </is>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5"/>
       <c r="K67" s="11">
-        <v>33.07169</v>
+        <v>33.31541</v>
       </c>
       <c r="L67" s="11">
-        <v>-97.2405</v>
+        <v>-96.7799</v>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">West</t>
+          <t xml:space="preserve">North</t>
         </is>
       </c>
       <c r="N67" s="5"/>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">14'' x 48''</t>
+          <t xml:space="preserve">10' ' x 30''</t>
         </is>
       </c>
       <c r="P67" s="5"/>
-      <c r="Q67" s="5"/>
+      <c r="Q67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TX-289 HV</t>
+        </is>
+      </c>
       <c r="R67" s="7">
-        <v>46328</v>
+        <v>46209</v>
       </c>
       <c r="S67" s="7">
-        <v>46397</v>
+        <v>46551</v>
       </c>
       <c r="T67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robson Ranch_GD.pdf</t>
+          <t xml:space="preserve">HEB Renewals RG_merged cosigned.pdf</t>
         </is>
       </c>
       <c r="U67" s="5">
-        <v>120067</v>
+        <v>105300</v>
       </c>
       <c r="V67" s="9">
-        <v>3293</v>
+        <v>2900</v>
       </c>
       <c r="W67" s="9"/>
       <c r="X67" s="5"/>
       <c r="Y67" s="5">
-        <v>4.3</v>
-      </c>
-      <c r="Z67" s="5"/>
-      <c r="AA67" s="5"/>
+        <v>3.8</v>
+      </c>
+      <c r="Z67" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">📐 Spec Sheet</t>
+        </is>
+      </c>
+      <c r="AA67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+        </is>
+      </c>
       <c r="AB67" s="5"/>
       <c r="AC67" s="7"/>
-      <c r="AD67" s="5"/>
+      <c r="AD67" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cowboys: Dak</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">290R</t>
+          <t xml:space="preserve">445R</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -7051,39 +7047,39 @@
       <c r="G68" s="4"/>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preston Rd.SB @Celina Storage</t>
+          <t xml:space="preserve">US 80 EB, next to Collins Rd. exit</t>
         </is>
       </c>
       <c r="I68" s="4"/>
       <c r="J68" s="4"/>
       <c r="K68" s="10">
-        <v>33.31541</v>
+        <v>32.78546</v>
       </c>
       <c r="L68" s="10">
-        <v>-96.7799</v>
+        <v>-96.568</v>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">North</t>
+          <t xml:space="preserve">West</t>
         </is>
       </c>
       <c r="N68" s="4"/>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10' ' x 30''</t>
+          <t xml:space="preserve">10'' x 40''</t>
         </is>
       </c>
       <c r="P68" s="4"/>
       <c r="Q68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">TX-289 HV</t>
+          <t xml:space="preserve">Blunting/Perm</t>
         </is>
       </c>
       <c r="R68" s="6">
         <v>46209</v>
       </c>
       <c r="S68" s="6">
-        <v>46551</v>
+        <v>46565</v>
       </c>
       <c r="T68" s="4" t="inlineStr">
         <is>
@@ -7091,15 +7087,15 @@
         </is>
       </c>
       <c r="U68" s="4">
-        <v>105300</v>
+        <v>217000</v>
       </c>
       <c r="V68" s="8">
-        <v>2900</v>
+        <v>2200</v>
       </c>
       <c r="W68" s="8"/>
       <c r="X68" s="4"/>
       <c r="Y68" s="4">
-        <v>3.8</v>
+        <v>7.5</v>
       </c>
       <c r="Z68" s="12" t="inlineStr">
         <is>
@@ -7108,110 +7104,12 @@
       </c>
       <c r="AA68" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">More Dinner. Less Dinero.</t>
+          <t xml:space="preserve">We have marinated meats</t>
         </is>
       </c>
       <c r="AB68" s="4"/>
       <c r="AC68" s="6"/>
       <c r="AD68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cowboys: Dak</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">445R</t>
-        </is>
-      </c>
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Reiss Group</t>
-        </is>
-      </c>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lisa@thereissgroup.net</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">North West</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bulletin</t>
-        </is>
-      </c>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">US 80 EB, next to Collins Rd. exit</t>
-        </is>
-      </c>
-      <c r="I69" s="5"/>
-      <c r="J69" s="5"/>
-      <c r="K69" s="11">
-        <v>32.78546</v>
-      </c>
-      <c r="L69" s="11">
-        <v>-96.568</v>
-      </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">West</t>
-        </is>
-      </c>
-      <c r="N69" s="5"/>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10'' x 40''</t>
-        </is>
-      </c>
-      <c r="P69" s="5"/>
-      <c r="Q69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Blunting/Perm</t>
-        </is>
-      </c>
-      <c r="R69" s="7">
-        <v>46209</v>
-      </c>
-      <c r="S69" s="7">
-        <v>46565</v>
-      </c>
-      <c r="T69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HEB Renewals RG_merged cosigned.pdf</t>
-        </is>
-      </c>
-      <c r="U69" s="5">
-        <v>217000</v>
-      </c>
-      <c r="V69" s="9">
-        <v>2200</v>
-      </c>
-      <c r="W69" s="9"/>
-      <c r="X69" s="5"/>
-      <c r="Y69" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="Z69" s="13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">📐 Spec Sheet</t>
-        </is>
-      </c>
-      <c r="AA69" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">We have marinated meats</t>
-        </is>
-      </c>
-      <c r="AB69" s="5"/>
-      <c r="AC69" s="7"/>
-      <c r="AD69" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Cowboys: DeMo</t>
         </is>
@@ -7257,17 +7155,17 @@
     <hyperlink ref="Z24" r:id="rIdH31"/>
     <hyperlink ref="Z25" r:id="rIdH32"/>
     <hyperlink ref="Z26" r:id="rIdH33"/>
-    <hyperlink ref="Z27" r:id="rIdH34"/>
-    <hyperlink ref="X28" r:id="rIdH35"/>
-    <hyperlink ref="Z28" r:id="rIdH36"/>
-    <hyperlink ref="X29" r:id="rIdH37"/>
+    <hyperlink ref="X27" r:id="rIdH34"/>
+    <hyperlink ref="Z27" r:id="rIdH35"/>
+    <hyperlink ref="X28" r:id="rIdH36"/>
+    <hyperlink ref="Z28" r:id="rIdH37"/>
     <hyperlink ref="Z29" r:id="rIdH38"/>
     <hyperlink ref="Z30" r:id="rIdH39"/>
-    <hyperlink ref="Z31" r:id="rIdH40"/>
-    <hyperlink ref="X32" r:id="rIdH41"/>
+    <hyperlink ref="X31" r:id="rIdH40"/>
+    <hyperlink ref="Z31" r:id="rIdH41"/>
     <hyperlink ref="Z32" r:id="rIdH42"/>
-    <hyperlink ref="Z33" r:id="rIdH43"/>
-    <hyperlink ref="X34" r:id="rIdH44"/>
+    <hyperlink ref="X33" r:id="rIdH43"/>
+    <hyperlink ref="Z33" r:id="rIdH44"/>
     <hyperlink ref="Z34" r:id="rIdH45"/>
     <hyperlink ref="Z35" r:id="rIdH46"/>
     <hyperlink ref="Z36" r:id="rIdH47"/>
@@ -7285,30 +7183,29 @@
     <hyperlink ref="Z48" r:id="rIdH59"/>
     <hyperlink ref="Z49" r:id="rIdH60"/>
     <hyperlink ref="Z50" r:id="rIdH61"/>
-    <hyperlink ref="Z51" r:id="rIdH62"/>
-    <hyperlink ref="X52" r:id="rIdH63"/>
-    <hyperlink ref="Z52" r:id="rIdH64"/>
-    <hyperlink ref="X53" r:id="rIdH65"/>
-    <hyperlink ref="Z53" r:id="rIdH66"/>
-    <hyperlink ref="X55" r:id="rIdH67"/>
-    <hyperlink ref="Z55" r:id="rIdH68"/>
-    <hyperlink ref="X56" r:id="rIdH69"/>
-    <hyperlink ref="Z56" r:id="rIdH70"/>
-    <hyperlink ref="X57" r:id="rIdH71"/>
-    <hyperlink ref="Z57" r:id="rIdH72"/>
-    <hyperlink ref="X58" r:id="rIdH73"/>
-    <hyperlink ref="Z58" r:id="rIdH74"/>
-    <hyperlink ref="X59" r:id="rIdH75"/>
+    <hyperlink ref="X51" r:id="rIdH62"/>
+    <hyperlink ref="Z51" r:id="rIdH63"/>
+    <hyperlink ref="X52" r:id="rIdH64"/>
+    <hyperlink ref="Z52" r:id="rIdH65"/>
+    <hyperlink ref="X54" r:id="rIdH66"/>
+    <hyperlink ref="Z54" r:id="rIdH67"/>
+    <hyperlink ref="X55" r:id="rIdH68"/>
+    <hyperlink ref="Z55" r:id="rIdH69"/>
+    <hyperlink ref="X56" r:id="rIdH70"/>
+    <hyperlink ref="Z56" r:id="rIdH71"/>
+    <hyperlink ref="X57" r:id="rIdH72"/>
+    <hyperlink ref="Z57" r:id="rIdH73"/>
+    <hyperlink ref="X58" r:id="rIdH74"/>
+    <hyperlink ref="Z58" r:id="rIdH75"/>
     <hyperlink ref="Z59" r:id="rIdH76"/>
-    <hyperlink ref="Z60" r:id="rIdH77"/>
-    <hyperlink ref="X63" r:id="rIdH78"/>
-    <hyperlink ref="Z63" r:id="rIdH79"/>
-    <hyperlink ref="X64" r:id="rIdH80"/>
+    <hyperlink ref="X62" r:id="rIdH77"/>
+    <hyperlink ref="Z62" r:id="rIdH78"/>
+    <hyperlink ref="X63" r:id="rIdH79"/>
+    <hyperlink ref="Z63" r:id="rIdH80"/>
     <hyperlink ref="Z64" r:id="rIdH81"/>
     <hyperlink ref="Z65" r:id="rIdH82"/>
-    <hyperlink ref="Z66" r:id="rIdH83"/>
+    <hyperlink ref="Z67" r:id="rIdH83"/>
     <hyperlink ref="Z68" r:id="rIdH84"/>
-    <hyperlink ref="Z69" r:id="rIdH85"/>
   </hyperlinks>
 </worksheet>
 </file>